--- a/data/trans_orig/P37C2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son seguras en 2023</t>
+          <t>Población según la creencia de que las vacunas son seguras en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>12821</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47444</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44358</t>
+          <t>43087</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34128</t>
+          <t>35047</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76659</t>
+          <t>76733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76321</t>
+          <t>77111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135159</t>
+          <t>135736</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41799</t>
+          <t>41112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76771</t>
+          <t>74780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127474</t>
+          <t>129879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198643</t>
+          <t>196992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227398</t>
+          <t>228893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>292736</t>
+          <t>293275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201135</t>
+          <t>201780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242482</t>
+          <t>243817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>450579</t>
+          <t>448410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>522913</t>
+          <t>525191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14291</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>876</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22656</t>
+          <t>20935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51359</t>
+          <t>51589</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>23929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68480</t>
+          <t>69275</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>67299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109721</t>
+          <t>110932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86365</t>
+          <t>85727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>294701</t>
+          <t>285440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171902</t>
+          <t>171792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>405119</t>
+          <t>412588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268062</t>
+          <t>264185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311886</t>
+          <t>313250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204601</t>
+          <t>209586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>401602</t>
+          <t>402140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>483286</t>
+          <t>471091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694474</t>
+          <t>691354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18063</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22722</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45643</t>
+          <t>45331</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19702</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33178</t>
+          <t>33199</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59635</t>
+          <t>58614</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96666</t>
+          <t>94842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133875</t>
+          <t>134600</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>89457</t>
+          <t>90039</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118963</t>
+          <t>120078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>196041</t>
+          <t>195887</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>246679</t>
+          <t>242383</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348335</t>
+          <t>350818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>392555</t>
+          <t>393700</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>403688</t>
+          <t>402419</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>435535</t>
+          <t>434108</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>760837</t>
+          <t>766712</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>816472</t>
+          <t>819892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>45210</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>58147</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41310</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>90393</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62349</t>
+          <t>65097</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204347</t>
+          <t>202014</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115092</t>
+          <t>114581</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155202</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157864</t>
+          <t>167387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>336822</t>
+          <t>339050</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>624945</t>
+          <t>626875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>801134</t>
+          <t>797226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>508177</t>
+          <t>506004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>556413</t>
+          <t>557733</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1158330</t>
+          <t>1154757</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1390421</t>
+          <t>1373269</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48324</t>
+          <t>47251</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>28427</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>43846</t>
+          <t>43746</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>69655</t>
+          <t>69914</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>98603</t>
+          <t>98114</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>133557</t>
+          <t>133404</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>107594</t>
+          <t>107511</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>136114</t>
+          <t>136437</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>214294</t>
+          <t>212998</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>259586</t>
+          <t>259310</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>376766</t>
+          <t>379412</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>416311</t>
+          <t>417309</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>380183</t>
+          <t>378405</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>411154</t>
+          <t>409581</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>769918</t>
+          <t>767571</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>817560</t>
+          <t>817251</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,36%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>333</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>35655</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>19287</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>60285</t>
+          <t>59263</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>84629</t>
+          <t>84188</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>30153</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>135226</t>
+          <t>132417</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>82146</t>
+          <t>82719</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>205199</t>
+          <t>204718</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>259785</t>
+          <t>259378</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>285900</t>
+          <t>286524</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>429866</t>
+          <t>430633</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>555995</t>
+          <t>561682</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>704587</t>
+          <t>705172</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>860898</t>
+          <t>859281</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -4822,97 +4822,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>1180</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>4152</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>1269</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>4760</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>4502</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>24602</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>41006</t>
+          <t>39496</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>43553</t>
+          <t>42941</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>64690</t>
+          <t>63834</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>67733</t>
+          <t>68531</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>90569</t>
+          <t>91015</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>117982</t>
+          <t>117098</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>147791</t>
+          <t>147141</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>201014</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>223908</t>
+          <t>223600</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>306664</t>
+          <t>305943</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>330520</t>
+          <t>331064</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>513950</t>
+          <t>515424</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>547596</t>
+          <t>548764</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22148</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,47 +5519,47 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>6149</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>22130</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>11948</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>21095</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>36024</t>
+          <t>36592</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>26297</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>50611</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>43826</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>71987</t>
+          <t>73593</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>145616</t>
+          <t>145680</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>222411</t>
+          <t>220376</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>123048</t>
+          <t>123261</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>180560</t>
+          <t>184498</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>289007</t>
+          <t>285418</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>389005</t>
+          <t>382375</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>541800</t>
+          <t>544855</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>763313</t>
+          <t>767920</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>624402</t>
+          <t>633279</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>910616</t>
+          <t>914965</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1254981</t>
+          <t>1242645</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1619107</t>
+          <t>1582515</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2418497</t>
+          <t>2417162</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2704114</t>
+          <t>2711381</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2563167</t>
+          <t>2572038</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2857237</t>
+          <t>2855380</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5046842</t>
+          <t>5079816</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5461346</t>
+          <t>5479821</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14234</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,57 +848,57 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2855</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8797</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2878</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10681</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25578</t>
+          <t>29214</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>52493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26816</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>17495</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>52394</t>
+          <t>59020</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35047</t>
+          <t>40937</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76733</t>
+          <t>84352</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>104312</t>
+          <t>108760</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77111</t>
+          <t>82499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135736</t>
+          <t>136660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57053</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41112</t>
+          <t>47627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74780</t>
+          <t>86117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>161365</t>
+          <t>173044</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129879</t>
+          <t>143930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>196992</t>
+          <t>210040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>262953</t>
+          <t>259039</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>228893</t>
+          <t>230991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>293275</t>
+          <t>288071</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>223216</t>
+          <t>262234</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201780</t>
+          <t>238204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243817</t>
+          <t>283241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>486169</t>
+          <t>521274</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>448410</t>
+          <t>479307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>525191</t>
+          <t>555290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>763886</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>763886</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>763886</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14048</t>
+          <t>20708</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>25445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34193</t>
+          <t>36438</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51589</t>
+          <t>53177</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>18374</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23929</t>
+          <t>28334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>54812</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32958</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69275</t>
+          <t>75784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88471</t>
+          <t>104192</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67299</t>
+          <t>83134</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110932</t>
+          <t>129204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>148700</t>
+          <t>92963</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>76223</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>285440</t>
+          <t>110186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>237171</t>
+          <t>197155</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171792</t>
+          <t>170669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>412588</t>
+          <t>230498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>290106</t>
+          <t>322281</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264185</t>
+          <t>294937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313250</t>
+          <t>346006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>341508</t>
+          <t>383794</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>209586</t>
+          <t>364116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>402140</t>
+          <t>402170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>631614</t>
+          <t>706075</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>471091</t>
+          <t>672322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>691354</t>
+          <t>736303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>420446</t>
+          <t>473885</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>420446</t>
+          <t>473885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>420446</t>
+          <t>473885</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>510643</t>
+          <t>500229</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>510643</t>
+          <t>500229</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>510643</t>
+          <t>500229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>931089</t>
+          <t>974114</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>931089</t>
+          <t>974114</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>931089</t>
+          <t>974114</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>13760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>40114</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45331</t>
+          <t>57473</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>14618</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>22453</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>54731</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33199</t>
+          <t>41747</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58614</t>
+          <t>71156</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>114663</t>
+          <t>134193</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94842</t>
+          <t>114618</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>134600</t>
+          <t>157091</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>104332</t>
+          <t>125460</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90039</t>
+          <t>109442</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>120078</t>
+          <t>143598</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>218995</t>
+          <t>259653</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>195887</t>
+          <t>233339</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242383</t>
+          <t>287692</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>372230</t>
+          <t>425300</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>350818</t>
+          <t>398537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>393700</t>
+          <t>448629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>418886</t>
+          <t>473406</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>402419</t>
+          <t>455408</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>434108</t>
+          <t>491464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>791116</t>
+          <t>898706</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>766712</t>
+          <t>866946</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>819892</t>
+          <t>927476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>533289</t>
+          <t>614925</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>533289</t>
+          <t>614925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>533289</t>
+          <t>614925</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>539945</t>
+          <t>618986</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>539945</t>
+          <t>618986</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>539945</t>
+          <t>618986</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1073234</t>
+          <t>1233911</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1073234</t>
+          <t>1233911</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1073234</t>
+          <t>1233911</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28876</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45210</t>
+          <t>46411</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38373</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27887</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58147</t>
+          <t>49570</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>56397</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90393</t>
+          <t>88194</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>139148</t>
+          <t>156223</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65097</t>
+          <t>136902</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>202014</t>
+          <t>178224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>136758</t>
+          <t>151580</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114581</t>
+          <t>133718</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155875</t>
+          <t>170008</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>275906</t>
+          <t>307803</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167387</t>
+          <t>279786</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>339050</t>
+          <t>335845</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>704970</t>
+          <t>496931</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>626875</t>
+          <t>472299</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>797226</t>
+          <t>519355</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>530228</t>
+          <t>538552</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>506004</t>
+          <t>518496</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>557733</t>
+          <t>556951</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1235197</t>
+          <t>1035482</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1154757</t>
+          <t>1003559</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1373269</t>
+          <t>1064236</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>882092</t>
+          <t>694551</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>882092</t>
+          <t>694551</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>882092</t>
+          <t>694551</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>708539</t>
+          <t>732398</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>708539</t>
+          <t>732398</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>708539</t>
+          <t>732398</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1590630</t>
+          <t>1426948</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1590630</t>
+          <t>1426948</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1590630</t>
+          <t>1426948</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,22 +3523,22 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -3566,22 +3566,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>17337</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>29479</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47251</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28427</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>56141</t>
+          <t>64701</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>50984</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>69914</t>
+          <t>81087</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>114088</t>
+          <t>128380</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>98114</t>
+          <t>110728</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>133404</t>
+          <t>149270</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>121498</t>
+          <t>133339</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>107511</t>
+          <t>119269</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>136437</t>
+          <t>150235</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>235587</t>
+          <t>261719</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>212998</t>
+          <t>236835</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>259310</t>
+          <t>288460</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>397927</t>
+          <t>425624</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>379412</t>
+          <t>404081</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>417309</t>
+          <t>446980</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>396073</t>
+          <t>442215</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>378405</t>
+          <t>424819</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>409581</t>
+          <t>456025</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>794001</t>
+          <t>867839</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>767571</t>
+          <t>840580</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>817251</t>
+          <t>894860</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>555078</t>
+          <t>602873</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>555078</t>
+          <t>602873</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>555078</t>
+          <t>602873</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>543928</t>
+          <t>606416</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>543928</t>
+          <t>606416</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>543928</t>
+          <t>606416</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1099006</t>
+          <t>1209289</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1099006</t>
+          <t>1209289</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1099006</t>
+          <t>1209289</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -4248,22 +4248,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>22602</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>35655</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>40963</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>71785</t>
+          <t>80271</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>59263</t>
+          <t>66389</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>84188</t>
+          <t>96221</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>84002</t>
+          <t>91593</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>78969</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>132417</t>
+          <t>103683</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>155787</t>
+          <t>171864</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>82719</t>
+          <t>153091</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>204718</t>
+          <t>190288</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>273511</t>
+          <t>300909</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>259378</t>
+          <t>286701</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>286524</t>
+          <t>315432</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>493257</t>
+          <t>315645</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>430633</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>561682</t>
+          <t>329132</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>766768</t>
+          <t>616554</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>705172</t>
+          <t>595399</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>859281</t>
+          <t>636636</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>366488</t>
+          <t>404599</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>366488</t>
+          <t>404599</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>366488</t>
+          <t>404599</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>601140</t>
+          <t>433064</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>601140</t>
+          <t>433064</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>601140</t>
+          <t>433064</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>967628</t>
+          <t>837663</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>967628</t>
+          <t>837663</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>967628</t>
+          <t>837663</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>533</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>14279</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>23307</t>
+          <t>26783</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>44634</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>53184</t>
+          <t>60168</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>42941</t>
+          <t>49178</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>63834</t>
+          <t>72641</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>78984</t>
+          <t>85356</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>68531</t>
+          <t>72776</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>91015</t>
+          <t>97861</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,27 +5226,27 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>132168</t>
+          <t>145524</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>117098</t>
+          <t>126246</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>147141</t>
+          <t>160762</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>213233</t>
+          <t>231374</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>201736</t>
+          <t>217806</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>223600</t>
+          <t>243536</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>319182</t>
+          <t>349099</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>305943</t>
+          <t>335793</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>331064</t>
+          <t>362631</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>532415</t>
+          <t>580474</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>515424</t>
+          <t>562267</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>548764</t>
+          <t>599659</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>279138</t>
+          <t>305888</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>279138</t>
+          <t>305888</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>279138</t>
+          <t>305888</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>421112</t>
+          <t>459447</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>421112</t>
+          <t>459447</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>421112</t>
+          <t>459447</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>765335</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>765335</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>765335</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,102 +5499,102 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>13719</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>23139</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>25098</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>16415</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>37097</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>11948</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>6149</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>24004</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>14807</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>36592</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>37186</t>
+          <t>42879</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>26297</t>
+          <t>31780</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>57825</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,27 +5647,27 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>64404</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>43826</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>73593</t>
+          <t>80757</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>184619</t>
+          <t>210190</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>145680</t>
+          <t>179670</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>220376</t>
+          <t>243005</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>152932</t>
+          <t>168289</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>123261</t>
+          <t>146101</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>184498</t>
+          <t>195503</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>337550</t>
+          <t>378479</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>285418</t>
+          <t>340740</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>382375</t>
+          <t>421575</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>685652</t>
+          <t>772187</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>544855</t>
+          <t>718689</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>767920</t>
+          <t>828294</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>731326</t>
+          <t>744575</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>633279</t>
+          <t>701194</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>914965</t>
+          <t>788062</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1416978</t>
+          <t>1516762</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1242645</t>
+          <t>1446286</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1582515</t>
+          <t>1581154</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2514931</t>
+          <t>2461459</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2417162</t>
+          <t>2396453</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2711381</t>
+          <t>2523718</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2722349</t>
+          <t>2764944</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2572038</t>
+          <t>2713611</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2855380</t>
+          <t>2814299</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>5237280</t>
+          <t>5226403</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5079816</t>
+          <t>5151168</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5479821</t>
+          <t>5304047</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3434444</t>
+          <t>3498094</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3434444</t>
+          <t>3498094</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3434444</t>
+          <t>3498094</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3638506</t>
+          <t>3713052</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3638506</t>
+          <t>3713052</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3638506</t>
+          <t>3713052</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7072950</t>
+          <t>7211146</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7072950</t>
+          <t>7211146</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7072950</t>
+          <t>7211146</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
